--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.51643230423362</v>
+        <v>12.10892024943796</v>
       </c>
       <c r="D2" t="n">
-        <v>74.38970399358814</v>
+        <v>12.08832689895807</v>
       </c>
       <c r="E2" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F2" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.00094893143132</v>
+        <v>10.88765420135759</v>
       </c>
       <c r="D3" t="n">
-        <v>66.8163153824495</v>
+        <v>10.85765124964805</v>
       </c>
       <c r="E3" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F3" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.23278695691735</v>
+        <v>4.425327880499069</v>
       </c>
       <c r="D4" t="n">
-        <v>26.30799290112553</v>
+        <v>4.275048846432898</v>
       </c>
       <c r="E4" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F4" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.44043358218035</v>
+        <v>8.846570457104308</v>
       </c>
       <c r="D5" t="n">
-        <v>54.69220516985822</v>
+        <v>8.88748334010196</v>
       </c>
       <c r="E5" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F5" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.74801803083853</v>
+        <v>3.696552930011261</v>
       </c>
       <c r="D6" t="n">
-        <v>22.24952697958141</v>
+        <v>3.61554813418198</v>
       </c>
       <c r="E6" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F6" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.23505411893377</v>
+        <v>8.813196294326739</v>
       </c>
       <c r="D7" t="n">
-        <v>54.12700491929466</v>
+        <v>8.795638299385383</v>
       </c>
       <c r="E7" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F7" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.21063512398489</v>
+        <v>9.621728207647545</v>
       </c>
       <c r="D8" t="n">
-        <v>59.2012873894078</v>
+        <v>9.620209200778769</v>
       </c>
       <c r="E8" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F8" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.63137220938415</v>
+        <v>8.065097984024924</v>
       </c>
       <c r="D9" t="n">
-        <v>49.5928835964873</v>
+        <v>8.058843584429187</v>
       </c>
       <c r="E9" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F9" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.850728129734085</v>
+        <v>0.7882433210817889</v>
       </c>
       <c r="D10" t="n">
-        <v>3.991197193884792</v>
+        <v>0.6485695440062788</v>
       </c>
       <c r="E10" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F10" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.275745505977993</v>
+        <v>1.507308644721424</v>
       </c>
       <c r="D11" t="n">
-        <v>10.04967890073138</v>
+        <v>1.633072821368849</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F11" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.59397918853032</v>
+        <v>3.509021618136178</v>
       </c>
       <c r="D12" t="n">
-        <v>21.99340347024354</v>
+        <v>3.573928063914575</v>
       </c>
       <c r="E12" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F12" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.42535074895493</v>
+        <v>4.619119496705177</v>
       </c>
       <c r="D13" t="n">
-        <v>28.53613923068962</v>
+        <v>4.637122624987063</v>
       </c>
       <c r="E13" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F13" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.65273610135584</v>
+        <v>4.006069616470325</v>
       </c>
       <c r="D14" t="n">
-        <v>25.27450389343485</v>
+        <v>4.107106882683163</v>
       </c>
       <c r="E14" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F14" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.56329678953997</v>
+        <v>4.479035728300246</v>
       </c>
       <c r="D15" t="n">
-        <v>27.36656350186705</v>
+        <v>4.447066569053396</v>
       </c>
       <c r="E15" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F15" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.8180656944218</v>
+        <v>1.757935675343542</v>
       </c>
       <c r="D16" t="n">
-        <v>10.7401587210803</v>
+        <v>1.745275792175549</v>
       </c>
       <c r="E16" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F16" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41274660258228</v>
+        <v>5.754571322919621</v>
       </c>
       <c r="D17" t="n">
-        <v>35.32834421926138</v>
+        <v>5.740855935629975</v>
       </c>
       <c r="E17" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F17" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.39083713426432</v>
+        <v>6.401011034317952</v>
       </c>
       <c r="D18" t="n">
-        <v>39.38639172375537</v>
+        <v>6.400288655110248</v>
       </c>
       <c r="E18" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F18" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.69104766337574</v>
+        <v>5.962295245298558</v>
       </c>
       <c r="D19" t="n">
-        <v>36.95367659245134</v>
+        <v>6.004972446273342</v>
       </c>
       <c r="E19" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F19" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>39.63877188438737</v>
+        <v>6.441300431212949</v>
       </c>
       <c r="D20" t="n">
-        <v>39.8444412340472</v>
+        <v>6.47472170053267</v>
       </c>
       <c r="E20" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F20" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>8.369242865214806</v>
+        <v>1.360001965597406</v>
       </c>
       <c r="D21" t="n">
-        <v>8.007462054972912</v>
+        <v>1.301212583933098</v>
       </c>
       <c r="E21" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F21" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>34.56794107051854</v>
+        <v>5.617290423959262</v>
       </c>
       <c r="D22" t="n">
-        <v>34.34489479511244</v>
+        <v>5.581045404205772</v>
       </c>
       <c r="E22" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F22" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>47.56363030677458</v>
+        <v>7.729089924850869</v>
       </c>
       <c r="D23" t="n">
-        <v>47.75743830380412</v>
+        <v>7.76058372436817</v>
       </c>
       <c r="E23" t="n">
-        <v>18.82125112444986</v>
+        <v>3.058453307723101</v>
       </c>
       <c r="F23" t="n">
-        <v>18.8617697750224</v>
+        <v>3.06503758844114</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
